--- a/src/main/resources/python/MultifacetedModeling/Results/OnAllTrain/DataDrivenNCOR/NCORs.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnAllTrain/DataDrivenNCOR/NCORs.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -54,15 +54,15 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -426,7 +426,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -608,7 +608,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -636,233 +636,233 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[6, 8, 9, 11, 28, 32, 36, 37]</t>
+          <t>[33, 36, 37]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['EN_M1', 'avg_EN_M', 'Radius_M1', 'avg_Radius_M', 'V', 'V_Na(2)O8', 'Min_BT', 'RT']</t>
+          <t>['V_Na(3)O5', 'Min_BT', 'RT']</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[17, 19, 20, 23, 25]</t>
+          <t>[35, 36, 37]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['EN_X1', 'avg_EN_X', 'Radius_X1', 'Valence_X1', 'avg_Valence_X']</t>
+          <t>['BT1', 'Min_BT', 'RT']</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[26, 28]</t>
+          <t>[4, 5, 7, 10, 13, 42]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['a', 'V']</t>
+          <t>['Occu_M1', 'Occu_M2', 'EN_M2', 'Radius_M2', 'Valence_M2', 'Entropy_M']</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[8, 11, 28, 32, 33, 36, 37]</t>
+          <t>[1, 3]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['avg_EN_M', 'avg_Radius_M', 'V', 'V_Na(2)O8', 'V_Na(3)O5', 'Min_BT', 'RT']</t>
+          <t>['Occu_18e', 'C_Na']</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[4, 5, 7, 10, 13, 42]</t>
+          <t>[27, 28]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['Occu_M1', 'Occu_M2', 'EN_M2', 'Radius_M2', 'Valence_M2', 'Entropy_M']</t>
+          <t>['c', 'V']</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[11, 28, 31, 32, 33, 35, 36, 37]</t>
+          <t>[6, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['avg_Radius_M', 'V', 'V_Na(1)O6', 'V_Na(2)O8', 'V_Na(3)O5', 'BT1', 'Min_BT', 'RT']</t>
+          <t>['EN_M1', 'avg_EN_M']</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[27, 28, 37]</t>
+          <t>[11, 32]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['c', 'V', 'RT']</t>
+          <t>['avg_Radius_M', 'V_Na(2)O8']</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 38, 41]</t>
+          <t>[1, 39]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['Occu_6b', 'Occu_18e', 'C_Na', 'Entropy_6b', 'Entropy_Na']</t>
+          <t>['Occu_18e', 'Entropy_18e']</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1, 3, 39, 41]</t>
+          <t>[39, 41]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['Occu_18e', 'C_Na', 'Entropy_18e', 'Entropy_Na']</t>
+          <t>['Entropy_18e', 'Entropy_Na']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[28, 29]</t>
+          <t>[8, 11]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['V', 'V_MO6']</t>
+          <t>['avg_EN_M', 'avg_Radius_M']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[19, 22]</t>
+          <t>[28, 32]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['avg_EN_X', 'avg_Radius_X']</t>
+          <t>['V', 'V_Na(2)O8']</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[6, 12]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['EN_M1', 'Valence_M1']</t>
+          <t>['Occu_6b', 'C_Na']</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[8, 11, 28, 32]</t>
+          <t>[6, 9]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['avg_EN_M', 'avg_Radius_M', 'V', 'V_Na(2)O8']</t>
+          <t>['EN_M1', 'Radius_M1']</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[26, 28]</t>
+          <t>[0, 3]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['a', 'V']</t>
+          <t>['Occu_6b', 'C_Na']</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[19, 22]</t>
+          <t>[12, 14]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['avg_EN_X', 'avg_Radius_X']</t>
+          <t>['Valence_M1', 'avg_Valence_M']</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[19, 22]</t>
+          <t>[6, 12]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['avg_EN_X', 'avg_Radius_X']</t>
+          <t>['EN_M1', 'Valence_M1']</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[11, 27]</t>
+          <t>[2, 40]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['avg_Radius_M', 'c']</t>
+          <t>['Occu_36f', 'Entropy_36f']</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[0, 3]</t>
+          <t>[12, 14]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['Occu_6b', 'C_Na']</t>
+          <t>['Valence_M1', 'avg_Valence_M']</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[6, 12]</t>
+          <t>[19, 22]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['EN_M1', 'Valence_M1']</t>
+          <t>['avg_EN_X', 'avg_Radius_X']</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1080,7 +1080,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1274,7 +1274,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1516,7 +1516,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1734,7 +1734,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1892,7 +1892,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2086,7 +2086,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2292,7 +2292,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2462,6 +2462,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>